--- a/backend/src/db/demo-docs/measurements-recovery-tee.xlsx
+++ b/backend/src/db/demo-docs/measurements-recovery-tee.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
